--- a/output/yearly_surface_area_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_14_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497653233529</v>
+        <v>10.84497643165092</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907263922387</v>
+        <v>37.78907228839147</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.679991306144545</v>
+        <v>8.592255907568084</v>
       </c>
       <c r="C2" t="n">
-        <v>6.390195806942488</v>
+        <v>3.917173339944773</v>
       </c>
       <c r="D2" t="n">
-        <v>22.99842171968578</v>
+        <v>32.07369749774329</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.47725255745097</v>
+        <v>23.6846633649543</v>
       </c>
       <c r="C3" t="n">
-        <v>19.11953654020664</v>
+        <v>20.39580855572748</v>
       </c>
       <c r="D3" t="n">
-        <v>66.6852128109646</v>
+        <v>90.60549562493813</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.41280136633594</v>
+        <v>40.8151790563569</v>
       </c>
       <c r="C4" t="n">
-        <v>65.14092367218436</v>
+        <v>62.74153228300516</v>
       </c>
       <c r="D4" t="n">
-        <v>91.10029646787852</v>
+        <v>93.49968785705774</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.77336481570179</v>
+        <v>51.51721078035138</v>
       </c>
       <c r="C5" t="n">
-        <v>98.59201319898595</v>
+        <v>77.43535017246718</v>
       </c>
       <c r="D5" t="n">
-        <v>70.29313562407164</v>
+        <v>62.0709986010046</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.80888765950392</v>
+        <v>47.65796055495717</v>
       </c>
       <c r="C6" t="n">
-        <v>94.06811977781665</v>
+        <v>64.24164277509429</v>
       </c>
       <c r="D6" t="n">
-        <v>49.34853010167018</v>
+        <v>43.14977509705582</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.92523261022377</v>
+        <v>33.65627479698915</v>
       </c>
       <c r="C7" t="n">
-        <v>74.91814905877834</v>
+        <v>56.8323928511436</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="C8" t="n">
-        <v>49.48499303256047</v>
+        <v>42.80910864368217</v>
       </c>
       <c r="D8" t="n">
-        <v>36.88426124855267</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.71556960413599</v>
+        <v>7.730074072224618</v>
       </c>
       <c r="C21" t="n">
-        <v>96.44462005169989</v>
+        <v>96.62592590280774</v>
       </c>
       <c r="D21" t="n">
-        <v>8.68001580465299</v>
+        <v>8.696333331252696</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.479534848028949</v>
+        <v>9.623090997027235</v>
       </c>
       <c r="C2" t="n">
-        <v>6.151631114810514</v>
+        <v>8.969247025998859</v>
       </c>
       <c r="D2" t="n">
-        <v>24.14215779513331</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.56560985083318</v>
+        <v>26.41883072128167</v>
       </c>
       <c r="C3" t="n">
-        <v>22.0991408225957</v>
+        <v>17.5438314748905</v>
       </c>
       <c r="D3" t="n">
-        <v>69.0512247781994</v>
+        <v>94.41467671741576</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.24313893995049</v>
+        <v>43.25285860600172</v>
       </c>
       <c r="C4" t="n">
-        <v>55.45401907438109</v>
+        <v>55.97729060074463</v>
       </c>
       <c r="D4" t="n">
-        <v>102.5484564471006</v>
+        <v>115.1963121209122</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.74944301790137</v>
+        <v>56.15596868291757</v>
       </c>
       <c r="C5" t="n">
-        <v>109.5875874865502</v>
+        <v>96.97212948697872</v>
       </c>
       <c r="D5" t="n">
-        <v>84.57756472086272</v>
+        <v>78.78525326580655</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.38249036069132</v>
+        <v>58.40515267334701</v>
       </c>
       <c r="C6" t="n">
-        <v>124.900888177392</v>
+        <v>92.45805354285189</v>
       </c>
       <c r="D6" t="n">
-        <v>59.41144407019999</v>
+        <v>52.1258943569844</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.90822410408209</v>
+        <v>45.45393695892307</v>
       </c>
       <c r="C7" t="n">
-        <v>104.0829281088383</v>
+        <v>74.97803566873739</v>
       </c>
       <c r="D7" t="n">
-        <v>44.67541102945535</v>
+        <v>41.80085375142069</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.03180114163017</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="C8" t="n">
-        <v>74.18576527141022</v>
+        <v>58.74778262212912</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.53749902030851</v>
+        <v>12.97968639784708</v>
       </c>
       <c r="C9" t="n">
-        <v>47.37030847761284</v>
+        <v>42.71093387325747</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1223,7 +1223,7 @@
         <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
         <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
         <v>33.56104526967722</v>
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.90552299774386</v>
+        <v>7.921558902447882</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7363700948241</v>
+        <v>105.9508503202404</v>
       </c>
       <c r="D21" t="n">
-        <v>9.881903747179825</v>
+        <v>9.901948628059852</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.954119899807657</v>
+        <v>10.79038901737669</v>
       </c>
       <c r="C2" t="n">
-        <v>10.54691558672348</v>
+        <v>10.99361079215578</v>
       </c>
       <c r="D2" t="n">
-        <v>22.75298479362408</v>
+        <v>27.98079131873834</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.32432089976671</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="C3" t="n">
-        <v>22.84036033930204</v>
+        <v>25.9770442543706</v>
       </c>
       <c r="D3" t="n">
-        <v>71.13252991120264</v>
+        <v>91.4497986505904</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.01791780505048</v>
+        <v>45.88197895797468</v>
       </c>
       <c r="C4" t="n">
-        <v>54.68825586506858</v>
+        <v>49.4938287618987</v>
       </c>
       <c r="D4" t="n">
-        <v>110.2699021410017</v>
+        <v>130.5881526280937</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.58392856651115</v>
+        <v>59.78843518863076</v>
       </c>
       <c r="C5" t="n">
-        <v>105.955120980837</v>
+        <v>99.77011044408214</v>
       </c>
       <c r="D5" t="n">
-        <v>99.30378028456489</v>
+        <v>98.29748888771192</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.25923211831272</v>
+        <v>66.85800040691205</v>
       </c>
       <c r="C6" t="n">
-        <v>146.1537624789269</v>
+        <v>119.4266629785118</v>
       </c>
       <c r="D6" t="n">
-        <v>69.43410638285567</v>
+        <v>61.98755004614362</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.71155576806323</v>
+        <v>56.17364014159399</v>
       </c>
       <c r="C7" t="n">
-        <v>139.2363681548039</v>
+        <v>101.9270101503123</v>
       </c>
       <c r="D7" t="n">
-        <v>50.60418541540184</v>
+        <v>46.59178254814513</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.12631096314512</v>
+        <v>36.63391558396972</v>
       </c>
       <c r="C8" t="n">
-        <v>102.558273924143</v>
+        <v>76.93956758182253</v>
       </c>
       <c r="D8" t="n">
-        <v>41.72427743048944</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.86249856814321</v>
+        <v>19.081248379741</v>
       </c>
       <c r="C9" t="n">
-        <v>67.8937442348924</v>
+        <v>56.46718270516377</v>
       </c>
       <c r="D9" t="n">
-        <v>37.82968428774233</v>
+        <v>37.38593432542277</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>44.84132639147307</v>
+        <v>42.27896488338889</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.686282702997524</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.07235589714055</v>
       </c>
       <c r="D11" t="n">
         <v>37.13853390395258</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
         <v>34.08137155292803</v>
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1604,7 +1604,7 @@
         <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.08103546321567</v>
+        <v>8.098374890673503</v>
       </c>
       <c r="C21" t="n">
-        <v>114.1446259179213</v>
+        <v>114.3895453307632</v>
       </c>
       <c r="D21" t="n">
-        <v>11.11142376192154</v>
+        <v>11.13526547467607</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.091163667774712</v>
+        <v>9.778207134298231</v>
       </c>
       <c r="C2" t="n">
-        <v>6.918376071827272</v>
+        <v>7.210936887692822</v>
       </c>
       <c r="D2" t="n">
-        <v>18.56583083501143</v>
+        <v>22.86294053649972</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.853703896534</v>
+        <v>33.99301425954581</v>
       </c>
       <c r="C3" t="n">
-        <v>37.5960283341316</v>
+        <v>40.15838984221578</v>
       </c>
       <c r="D3" t="n">
-        <v>79.08468631560181</v>
+        <v>100.3444328510665</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.37304843208056</v>
+        <v>28.71612034921921</v>
       </c>
       <c r="C4" t="n">
-        <v>84.38710566623882</v>
+        <v>78.31205087235958</v>
       </c>
       <c r="D4" t="n">
-        <v>108.2278669161684</v>
+        <v>121.3351805155675</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.55689729468198</v>
+        <v>37.65002445786519</v>
       </c>
       <c r="C5" t="n">
-        <v>87.3264582927538</v>
+        <v>71.34851440613696</v>
       </c>
       <c r="D5" t="n">
-        <v>69.11503837897546</v>
+        <v>64.40264939859077</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.98119222936585</v>
+        <v>34.85793398698726</v>
       </c>
       <c r="C6" t="n">
-        <v>91.69327208124361</v>
+        <v>67.09951034215676</v>
       </c>
       <c r="D6" t="n">
-        <v>33.32837106377072</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.60099382591507</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="C7" t="n">
-        <v>72.10347839070273</v>
+        <v>54.07760879302705</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>28.44613973055133</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>49.98568436172635</v>
+        <v>41.55738032076748</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D10" t="n">
         <v>29.04009709162065</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>27.77167905773377</v>
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1901,7 +1901,7 @@
         <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>18.41660518396592</v>
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.231332605303753</v>
+        <v>5.769731257858504</v>
       </c>
       <c r="C2" t="n">
-        <v>3.332051708213675</v>
+        <v>3.682535638629786</v>
       </c>
       <c r="D2" t="n">
-        <v>13.72483290537041</v>
+        <v>16.99797975132928</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.82701678207009</v>
+        <v>34.96003574822892</v>
       </c>
       <c r="C3" t="n">
-        <v>32.62838495064275</v>
+        <v>34.46425315758428</v>
       </c>
       <c r="D3" t="n">
-        <v>77.14082586119314</v>
+        <v>97.37464604571989</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.33247798103695</v>
+        <v>44.96306310679967</v>
       </c>
       <c r="C4" t="n">
-        <v>92.40209392370978</v>
+        <v>92.46590752448584</v>
       </c>
       <c r="D4" t="n">
-        <v>120.9267734706009</v>
+        <v>140.2367690654314</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>42.26423866782519</v>
       </c>
       <c r="C5" t="n">
-        <v>122.0803270230909</v>
+        <v>107.5013736150258</v>
       </c>
       <c r="D5" t="n">
-        <v>87.67006998924018</v>
+        <v>86.98284659626741</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.97868895460962</v>
+        <v>42.2642386678252</v>
       </c>
       <c r="C6" t="n">
-        <v>115.119735799981</v>
+        <v>88.71464954655879</v>
       </c>
       <c r="D6" t="n">
-        <v>41.57996051796516</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.58292145661112</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="C7" t="n">
-        <v>97.31574118346508</v>
+        <v>72.22325161062085</v>
       </c>
       <c r="D7" t="n">
-        <v>31.91956310817654</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>66.67539533392211</v>
+        <v>54.07466354991431</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>40.38124657107979</v>
+        <v>37.94062177832222</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2198,7 +2198,7 @@
         <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>15.70599977254047</v>
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.115887286830128</v>
+        <v>6.029894399483909</v>
       </c>
       <c r="C2" t="n">
-        <v>5.418265579738146</v>
+        <v>6.700428081484481</v>
       </c>
       <c r="D2" t="n">
-        <v>23.13292115516759</v>
+        <v>23.8986843644801</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.18335014098268</v>
+        <v>27.13059780686061</v>
       </c>
       <c r="C3" t="n">
-        <v>21.60335823195106</v>
+        <v>23.50304003966864</v>
       </c>
       <c r="D3" t="n">
-        <v>70.60238615090937</v>
+        <v>88.88743714250622</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.44131310748811</v>
+        <v>55.90071427981338</v>
       </c>
       <c r="C4" t="n">
-        <v>87.43739578333367</v>
+        <v>89.08378668335557</v>
       </c>
       <c r="D4" t="n">
-        <v>131.0093223932156</v>
+        <v>155.4882196509056</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.44800541496859</v>
+        <v>54.41336650787948</v>
       </c>
       <c r="C5" t="n">
-        <v>146.746738092292</v>
+        <v>139.678154621715</v>
       </c>
       <c r="D5" t="n">
-        <v>108.6303834749096</v>
+        <v>114.1527143112979</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.8151790563569</v>
+        <v>50.07305990740432</v>
       </c>
       <c r="C6" t="n">
-        <v>155.0896300829814</v>
+        <v>129.8518418499087</v>
       </c>
       <c r="D6" t="n">
-        <v>56.714583126634</v>
+        <v>53.85671555957153</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.98511922018283</v>
+        <v>34.55457394637499</v>
       </c>
       <c r="C7" t="n">
-        <v>131.5708820800448</v>
+        <v>99.83097880174539</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C8" t="n">
-        <v>96.29963230956963</v>
+        <v>74.18576527141022</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87596529856218</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>59.57343244140068</v>
+        <v>51.58593311964863</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>38.57777603837842</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2467,7 +2467,7 @@
         <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
         <v>29.50740899884213</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2509,7 +2509,7 @@
         <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2565,7 +2565,7 @@
         <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.953097094374406</v>
+        <v>3.523492510541802</v>
       </c>
       <c r="C2" t="n">
-        <v>2.444551783574558</v>
+        <v>3.025746424488669</v>
       </c>
       <c r="D2" t="n">
-        <v>15.94849145548943</v>
+        <v>16.53950357344601</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.07183181332604</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="C3" t="n">
-        <v>22.59983215176158</v>
+        <v>26.23229865747478</v>
       </c>
       <c r="D3" t="n">
-        <v>73.95014582239099</v>
+        <v>90.17843537359077</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.04865508351838</v>
+        <v>61.6056501891916</v>
       </c>
       <c r="C4" t="n">
-        <v>83.73620693832321</v>
+        <v>86.11007288719199</v>
       </c>
       <c r="D4" t="n">
-        <v>138.3478864824605</v>
+        <v>165.4814295324339</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.04963683122264</v>
+        <v>55.93507544946203</v>
       </c>
       <c r="C5" t="n">
-        <v>171.1186248502191</v>
+        <v>167.2652651110504</v>
       </c>
       <c r="D5" t="n">
-        <v>117.3433943501</v>
+        <v>124.26471566504</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.34095385747668</v>
+        <v>42.7070068824405</v>
       </c>
       <c r="C6" t="n">
-        <v>191.8796435519264</v>
+        <v>157.2632195001838</v>
       </c>
       <c r="D6" t="n">
-        <v>55.70829172978102</v>
+        <v>52.93092747446678</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>10.89936301254809</v>
       </c>
       <c r="C7" t="n">
-        <v>135.5832849473015</v>
+        <v>103.4241753992887</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>75.02025082002001</v>
+        <v>62.0022762617073</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -2764,7 +2764,7 @@
         <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
         <v>23.63361248433346</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2806,7 +2806,7 @@
         <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>12.90016483380309</v>
@@ -2862,7 +2862,7 @@
         <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.638356991938679</v>
+        <v>4.489532251520663</v>
       </c>
       <c r="C2" t="n">
-        <v>3.521529015133309</v>
+        <v>8.306567325632262</v>
       </c>
       <c r="D2" t="n">
-        <v>13.47056024997049</v>
+        <v>14.40027532589222</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.16800203061322</v>
+        <v>19.55150553007523</v>
       </c>
       <c r="C3" t="n">
-        <v>15.7128720064702</v>
+        <v>18.62866268808323</v>
       </c>
       <c r="D3" t="n">
-        <v>70.40603661006001</v>
+        <v>83.75780538781663</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.32568786256524</v>
+        <v>57.68749510154258</v>
       </c>
       <c r="C4" t="n">
-        <v>69.76102836836986</v>
+        <v>76.37211740876788</v>
       </c>
       <c r="D4" t="n">
-        <v>142.9297030181804</v>
+        <v>171.6968742480204</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.7443954106599</v>
+        <v>71.96210672129121</v>
       </c>
       <c r="C5" t="n">
-        <v>164.4427404613408</v>
+        <v>164.6145463095839</v>
       </c>
       <c r="D5" t="n">
-        <v>136.6101930459437</v>
+        <v>150.2564861349744</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.67933802027235</v>
+        <v>56.35231822376692</v>
       </c>
       <c r="C6" t="n">
-        <v>232.9765841994021</v>
+        <v>207.8595509339517</v>
       </c>
       <c r="D6" t="n">
-        <v>75.19009317285472</v>
+        <v>74.46556336712058</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.78065365579224</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="C7" t="n">
-        <v>198.5241120142688</v>
+        <v>159.1187226612103</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>39.94436884268997</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>7.093127163183205</v>
       </c>
       <c r="C8" t="n">
-        <v>120.6666103289755</v>
+        <v>93.71272710887928</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>54.0265579124062</v>
+        <v>47.8140584399324</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
         <v>24.34439782220815</v>
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
         <v>21.91359050649305</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.86995163914969</v>
+      </c>
+      <c r="D13" t="n">
         <v>16.1301147807751</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
         <v>14.74977750860408</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.608503650183775</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C2" t="n">
-        <v>2.033199495495144</v>
+        <v>4.214642894331557</v>
       </c>
       <c r="D2" t="n">
-        <v>10.60582044897829</v>
+        <v>10.99950127838126</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.17152811080271</v>
+        <v>17.97089172623786</v>
       </c>
       <c r="C3" t="n">
-        <v>15.06491852166731</v>
+        <v>25.29472959991907</v>
       </c>
       <c r="D3" t="n">
-        <v>66.74411767321941</v>
+        <v>77.78877934599603</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.50963453615788</v>
+        <v>51.20403326269664</v>
       </c>
       <c r="C4" t="n">
-        <v>57.43224069843841</v>
+        <v>65.17921183264998</v>
       </c>
       <c r="D4" t="n">
-        <v>145.3418571275148</v>
+        <v>174.3132318798382</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.14400778401735</v>
+        <v>79.86517574047804</v>
       </c>
       <c r="C5" t="n">
-        <v>155.7051858935442</v>
+        <v>160.8593613408399</v>
       </c>
       <c r="D5" t="n">
-        <v>149.6919812050324</v>
+        <v>169.2778479047563</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.40765594810324</v>
+        <v>67.34102027740147</v>
       </c>
       <c r="C6" t="n">
-        <v>254.6722267155524</v>
+        <v>236.2369683252058</v>
       </c>
       <c r="D6" t="n">
-        <v>90.76748399613888</v>
+        <v>89.88194756690825</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>23.41566449399068</v>
       </c>
       <c r="C7" t="n">
-        <v>251.2243287782375</v>
+        <v>208.1658562176767</v>
       </c>
       <c r="D7" t="n">
-        <v>47.07087542781757</v>
+        <v>45.33416373900496</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>159.8874311136355</v>
+        <v>124.2548981879975</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>67.11718180083317</v>
+        <v>57.57655761096267</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
         <v>11.67690719431156</v>
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.322635141798706</v>
+        <v>6.255696371460675</v>
       </c>
       <c r="C2" t="n">
-        <v>12.73326772408113</v>
+        <v>8.572620953483149</v>
       </c>
       <c r="D2" t="n">
-        <v>18.95067593507618</v>
+        <v>11.72403108411541</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.55517047898496</v>
+        <v>14.5887708851076</v>
       </c>
       <c r="C3" t="n">
-        <v>11.62880155680347</v>
+        <v>20.86704745376596</v>
       </c>
       <c r="D3" t="n">
-        <v>60.60819452167684</v>
+        <v>70.51402885752715</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.69808903764427</v>
+        <v>43.07418052382881</v>
       </c>
       <c r="C4" t="n">
-        <v>48.16650586575701</v>
+        <v>64.08161789930206</v>
       </c>
       <c r="D4" t="n">
-        <v>145.2525180864283</v>
+        <v>171.3522808038298</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.50587177625693</v>
+        <v>79.52156404399165</v>
       </c>
       <c r="C5" t="n">
-        <v>133.345881929323</v>
+        <v>142.5006792714246</v>
       </c>
       <c r="D5" t="n">
-        <v>163.8291481461865</v>
+        <v>188.0046853632642</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.95358978712248</v>
+        <v>82.8781594448115</v>
       </c>
       <c r="C6" t="n">
-        <v>252.6998955777206</v>
+        <v>245.2533392410085</v>
       </c>
       <c r="D6" t="n">
-        <v>110.3700404068349</v>
+        <v>113.9121861237574</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.27321326588365</v>
+        <v>42.81892612072463</v>
       </c>
       <c r="C7" t="n">
-        <v>301.1697614840897</v>
+        <v>266.2558678779604</v>
       </c>
       <c r="D7" t="n">
-        <v>57.79057861048849</v>
+        <v>56.11375353163493</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>232.1538796232433</v>
+        <v>184.2544091330414</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>117.5937400146829</v>
+        <v>94.96249193638545</v>
       </c>
       <c r="D9" t="n">
         <v>34.27968458918587</v>
@@ -3694,10 +3694,10 @@
         <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>49.82369599052563</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
-        <v>27.75891633757857</v>
+        <v>27.47420950334699</v>
       </c>
     </row>
     <row r="11">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
         <v>16.91060420565131</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
         <v>11.98419422574081</v>
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.011822030179967</v>
+        <v>6.44517367838031</v>
       </c>
       <c r="C2" t="n">
-        <v>4.417864669110647</v>
+        <v>3.604977569994288</v>
       </c>
       <c r="D2" t="n">
-        <v>12.29737174339555</v>
+        <v>5.711808143307943</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.057162351024567</v>
+        <v>4.426700398448868</v>
       </c>
       <c r="C2" t="n">
-        <v>7.029313562407163</v>
+        <v>4.799764526062656</v>
       </c>
       <c r="D2" t="n">
-        <v>13.94867138193868</v>
+        <v>8.629562320329464</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.77668560724624</v>
+        <v>20.5136182802371</v>
       </c>
       <c r="C3" t="n">
-        <v>25.5008966178109</v>
+        <v>27.91108723173682</v>
       </c>
       <c r="D3" t="n">
-        <v>67.46570223584081</v>
+        <v>75.8694625841935</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.35045253934966</v>
+        <v>60.16346281165303</v>
       </c>
       <c r="C4" t="n">
-        <v>70.64165605907924</v>
+        <v>89.81126173220245</v>
       </c>
       <c r="D4" t="n">
-        <v>150.7021995927024</v>
+        <v>175.5001648542726</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.57639338004667</v>
+        <v>49.62734644967627</v>
       </c>
       <c r="C5" t="n">
-        <v>206.0933868140117</v>
+        <v>210.167639786636</v>
       </c>
       <c r="D5" t="n">
-        <v>152.4899621621358</v>
+        <v>171.1922559280376</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.89690079552086</v>
+        <v>26.56609287691869</v>
       </c>
       <c r="C6" t="n">
-        <v>252.8206505453429</v>
+        <v>225.852041109683</v>
       </c>
       <c r="D6" t="n">
-        <v>86.78257006460107</v>
+        <v>87.58760318208346</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.126506585127596</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>163.2508987483851</v>
+        <v>129.5347373414369</v>
       </c>
       <c r="D7" t="n">
-        <v>35.63253292563798</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>86.61959994569608</v>
+        <v>69.9298889735003</v>
       </c>
       <c r="D8" t="n">
         <v>25.20146356801562</v>
@@ -4302,10 +4302,10 @@
         <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>21.1890607007589</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
         <v>13.66887328622834</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
         <v>9.886199381765381</v>
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.53116656572653</v>
       </c>
     </row>
     <row r="15">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.658212930201868</v>
+        <v>6.624833508257476</v>
       </c>
       <c r="C2" t="n">
-        <v>3.046363126277853</v>
+        <v>2.287472150895068</v>
       </c>
       <c r="D2" t="n">
-        <v>19.05474119172634</v>
+        <v>12.52906420159779</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.65196259107789</v>
+        <v>13.69047173572177</v>
       </c>
       <c r="C3" t="n">
-        <v>11.13301896615883</v>
+        <v>9.228428419920018</v>
       </c>
       <c r="D3" t="n">
-        <v>13.46466976374501</v>
+        <v>8.163232160812228</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39827202397852</v>
+        <v>13.39929799056473</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14389471376991</v>
+        <v>70.14926595060361</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57626729693865</v>
+        <v>1.576387998889969</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.181263472387165</v>
+        <v>4.641703145678919</v>
       </c>
       <c r="C2" t="n">
-        <v>3.742422248588841</v>
+        <v>3.076797305109504</v>
       </c>
       <c r="D2" t="n">
-        <v>20.01194520336698</v>
+        <v>13.48234122242145</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.02488784997144</v>
+        <v>19.22752878767378</v>
       </c>
       <c r="C3" t="n">
-        <v>11.59934912567607</v>
+        <v>9.036987617591889</v>
       </c>
       <c r="D3" t="n">
-        <v>26.21757244191107</v>
+        <v>16.71425466480195</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.45641487148353</v>
+        <v>15.88958659323463</v>
       </c>
       <c r="C4" t="n">
-        <v>17.52321477310132</v>
+        <v>14.83028082035232</v>
       </c>
       <c r="D4" t="n">
-        <v>22.1305567491316</v>
+        <v>19.34828375529614</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
         <v>34.77743067523902</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4910,7 +4910,7 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4423420935479</v>
+        <v>15.44569776264674</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1520137850567</v>
+        <v>86.17073488634499</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251019388115347</v>
+        <v>3.251725844767735</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.037347470490384</v>
+        <v>6.396086293167969</v>
       </c>
       <c r="C2" t="n">
-        <v>7.28554971321558</v>
+        <v>3.163191103083223</v>
       </c>
       <c r="D2" t="n">
-        <v>18.87115437103219</v>
+        <v>24.12055934563989</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.02703127182918</v>
+        <v>17.47020039707199</v>
       </c>
       <c r="C3" t="n">
-        <v>13.39594742444773</v>
+        <v>10.85322087044849</v>
       </c>
       <c r="D3" t="n">
-        <v>36.14304173184632</v>
+        <v>23.62084976417826</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.07874510498477</v>
+        <v>28.33323874456295</v>
       </c>
       <c r="C4" t="n">
-        <v>24.31298189567226</v>
+        <v>19.50143639715864</v>
       </c>
       <c r="D4" t="n">
-        <v>30.28593492830985</v>
+        <v>23.20262524216912</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.31464229144449</v>
+        <v>13.98990478551705</v>
       </c>
       <c r="C5" t="n">
-        <v>20.7148765596077</v>
+        <v>18.13778883595982</v>
       </c>
       <c r="D5" t="n">
-        <v>30.38509144643879</v>
+        <v>29.77149913128453</v>
       </c>
     </row>
     <row r="6">
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
         <v>37.42913122440964</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,10 +5274,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>45.77987719673301</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73973046443908</v>
+        <v>16.74713043816062</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1123558330784</v>
+        <v>102.1574956727798</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021919139331724</v>
+        <v>5.024139131448187</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.670173829102077</v>
+        <v>6.252751128347935</v>
       </c>
       <c r="C2" t="n">
-        <v>5.422192570555134</v>
+        <v>4.73104218676538</v>
       </c>
       <c r="D2" t="n">
-        <v>29.25411809114646</v>
+        <v>22.66659099565036</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.70443718775948</v>
+        <v>20.01783568959246</v>
       </c>
       <c r="C3" t="n">
-        <v>22.13841073076557</v>
+        <v>11.68770641905828</v>
       </c>
       <c r="D3" t="n">
-        <v>42.44586199311085</v>
+        <v>36.69772918474577</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.21837426316607</v>
+        <v>31.60049510429634</v>
       </c>
       <c r="C4" t="n">
-        <v>29.55845987946297</v>
+        <v>23.85352397008475</v>
       </c>
       <c r="D4" t="n">
-        <v>40.68755185480481</v>
+        <v>29.23939187558275</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.74004214701963</v>
+        <v>28.44613973055134</v>
       </c>
       <c r="C5" t="n">
-        <v>34.01755795215198</v>
+        <v>27.80800372279091</v>
       </c>
       <c r="D5" t="n">
-        <v>34.53297549688156</v>
+        <v>31.56318869153496</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.62643715076748</v>
+        <v>12.63901994447344</v>
       </c>
       <c r="C6" t="n">
-        <v>22.98369550412208</v>
+        <v>21.1321193339126</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
         <v>40.00425545264903</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>47.29864089520282</v>
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07338241943895</v>
+        <v>18.08518927328956</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9073043553875</v>
+        <v>117.9843300209843</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885098064548172</v>
+        <v>6.889595913634118</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.913066422678538</v>
+        <v>6.803511590430396</v>
       </c>
       <c r="C2" t="n">
-        <v>9.134180640312323</v>
+        <v>8.620726590991241</v>
       </c>
       <c r="D2" t="n">
-        <v>22.65088303238241</v>
+        <v>35.35568007304038</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.5740446695439</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="C3" t="n">
-        <v>20.238728923048</v>
+        <v>14.75566799482956</v>
       </c>
       <c r="D3" t="n">
-        <v>51.96390598578368</v>
+        <v>43.62395923820702</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.21989579021806</v>
+        <v>26.30396623988479</v>
       </c>
       <c r="C4" t="n">
-        <v>37.12675293150163</v>
+        <v>22.64106555533994</v>
       </c>
       <c r="D4" t="n">
-        <v>45.1545039091278</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.91122610045706</v>
+        <v>23.48831382410494</v>
       </c>
       <c r="C5" t="n">
-        <v>33.4285093296039</v>
+        <v>27.43984833369836</v>
       </c>
       <c r="D5" t="n">
-        <v>33.60031517784709</v>
+        <v>28.44613973055134</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.15600007398401</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="C6" t="n">
-        <v>26.84785446803753</v>
+        <v>22.58117894538089</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>30.30949687321178</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>18.77592484372025</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
         <v>30.12492830481337</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
         <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>32.32797015314322</v>
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5983,10 +5983,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.067407598288812</v>
+        <v>7.074682935400947</v>
       </c>
       <c r="C21" t="n">
-        <v>67.14037218374371</v>
+        <v>67.20948788630899</v>
       </c>
       <c r="D21" t="n">
-        <v>5.300555698716609</v>
+        <v>5.30601220155071</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.822344723260333</v>
+        <v>6.222316949516284</v>
       </c>
       <c r="C2" t="n">
-        <v>6.229189183446011</v>
+        <v>7.123561342014856</v>
       </c>
       <c r="D2" t="n">
-        <v>21.6082669704723</v>
+        <v>35.20056393576939</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.48140053244621</v>
+        <v>22.03532722181966</v>
       </c>
       <c r="C3" t="n">
-        <v>30.5470798176395</v>
+        <v>27.37112599440108</v>
       </c>
       <c r="D3" t="n">
-        <v>58.84104865403258</v>
+        <v>63.77433086787281</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.50816976236813</v>
+        <v>32.92781800043802</v>
       </c>
       <c r="C4" t="n">
-        <v>46.02236887968198</v>
+        <v>31.97061398879738</v>
       </c>
       <c r="D4" t="n">
-        <v>62.76705772331557</v>
+        <v>51.16574510223102</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.397052345339</v>
+        <v>33.45305302221007</v>
       </c>
       <c r="C5" t="n">
-        <v>55.68963852340033</v>
+        <v>36.59464567579986</v>
       </c>
       <c r="D5" t="n">
-        <v>42.97600575340413</v>
+        <v>35.46563581591603</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.85664913964674</v>
+        <v>24.87552333020568</v>
       </c>
       <c r="C6" t="n">
-        <v>42.86801350593698</v>
+        <v>35.42145716922493</v>
       </c>
       <c r="D6" t="n">
-        <v>35.46170882509904</v>
+        <v>33.16736444027425</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>30.48228446915921</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>21.86352137357647</v>
+        <v>21.27938148954961</v>
       </c>
       <c r="D8" t="n">
         <v>32.04424506661589</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>23.62968549351647</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6241,7 +6241,7 @@
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295227942476858</v>
+        <v>7.305152462060006</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51179688881662</v>
+        <v>77.61724490938757</v>
       </c>
       <c r="D21" t="n">
-        <v>6.38332444966725</v>
+        <v>6.392008404302505</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.980986940720816</v>
+        <v>7.343472827766142</v>
       </c>
       <c r="C2" t="n">
-        <v>3.514656781203581</v>
+        <v>3.945644023367931</v>
       </c>
       <c r="D2" t="n">
-        <v>22.94148035283946</v>
+        <v>39.48294742169397</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.70581984609123</v>
+        <v>21.88806506618264</v>
       </c>
       <c r="C3" t="n">
-        <v>26.63481521621597</v>
+        <v>27.62638039750524</v>
       </c>
       <c r="D3" t="n">
-        <v>63.33745313948297</v>
+        <v>77.9311327631118</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.98337670895259</v>
+        <v>39.19431359664541</v>
       </c>
       <c r="C4" t="n">
-        <v>64.61765214582081</v>
+        <v>54.25432337979149</v>
       </c>
       <c r="D4" t="n">
-        <v>77.57181310335747</v>
+        <v>72.72197944437823</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.17111150464198</v>
+        <v>42.48513190128072</v>
       </c>
       <c r="C5" t="n">
-        <v>73.11566027378122</v>
+        <v>49.57825906446394</v>
       </c>
       <c r="D5" t="n">
-        <v>56.57321145722246</v>
+        <v>46.4612101034803</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.11452999069417</v>
+        <v>36.70951015719674</v>
       </c>
       <c r="C6" t="n">
-        <v>68.870583200618</v>
+        <v>48.66425195181016</v>
       </c>
       <c r="D6" t="n">
-        <v>40.97618567985338</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.40326162673396</v>
+        <v>22.0382724649324</v>
       </c>
       <c r="C7" t="n">
-        <v>48.38838084691679</v>
+        <v>40.78278138211675</v>
       </c>
       <c r="D7" t="n">
-        <v>37.12969817461437</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>32.29459073119883</v>
+        <v>29.37389131106456</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>26.29218526743382</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
         <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -6552,7 +6552,7 @@
         <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6636,7 +6636,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.511853903088448</v>
+        <v>7.52449537157027</v>
       </c>
       <c r="C21" t="n">
-        <v>87.32530162340321</v>
+        <v>87.47225869450439</v>
       </c>
       <c r="D21" t="n">
-        <v>7.511853903088448</v>
+        <v>7.52449537157027</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_14_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497643165092</v>
+        <v>10.84497625627163</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907228839147</v>
+        <v>37.78907167728637</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.592255907568084</v>
+        <v>5.191481860057134</v>
       </c>
       <c r="C2" t="n">
-        <v>3.917173339944773</v>
+        <v>10.54004335279376</v>
       </c>
       <c r="D2" t="n">
-        <v>32.07369749774329</v>
+        <v>26.26371458401067</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.6846633649543</v>
+        <v>17.50456156672063</v>
       </c>
       <c r="C3" t="n">
-        <v>20.39580855572748</v>
+        <v>31.15576339427253</v>
       </c>
       <c r="D3" t="n">
-        <v>90.60549562493813</v>
+        <v>71.62831250184728</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.8151790563569</v>
+        <v>37.95632974159018</v>
       </c>
       <c r="C4" t="n">
-        <v>62.74153228300516</v>
+        <v>53.02910224489146</v>
       </c>
       <c r="D4" t="n">
-        <v>93.49968785705774</v>
+        <v>90.37282141903162</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.51721078035138</v>
+        <v>44.62043315801754</v>
       </c>
       <c r="C5" t="n">
-        <v>77.43535017246718</v>
+        <v>84.45484625783187</v>
       </c>
       <c r="D5" t="n">
-        <v>62.0709986010046</v>
+        <v>68.74688298988291</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.65796055495717</v>
+        <v>39.40637110076273</v>
       </c>
       <c r="C6" t="n">
-        <v>64.24164277509429</v>
+        <v>94.83290123942491</v>
       </c>
       <c r="D6" t="n">
-        <v>43.14977509705582</v>
+        <v>46.73217246985243</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.65627479698915</v>
+        <v>28.38625312059227</v>
       </c>
       <c r="C7" t="n">
-        <v>56.8323928511436</v>
+        <v>76.29554108783661</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.35729941108361</v>
+        <v>14.68694565553228</v>
       </c>
       <c r="C8" t="n">
-        <v>42.80910864368217</v>
+        <v>46.98153638673111</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.542186774651494</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -912,7 +912,7 @@
         <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.730074072224618</v>
+        <v>7.724119341972541</v>
       </c>
       <c r="C21" t="n">
-        <v>96.62592590280774</v>
+        <v>96.55149177465677</v>
       </c>
       <c r="D21" t="n">
-        <v>8.696333331252696</v>
+        <v>8.689634259719108</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.623090997027235</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C2" t="n">
-        <v>8.969247025998859</v>
+        <v>14.31584502332699</v>
       </c>
       <c r="D2" t="n">
-        <v>23.93500902953724</v>
+        <v>24.68113728476482</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.41883072128167</v>
+        <v>17.63709750679395</v>
       </c>
       <c r="C3" t="n">
-        <v>17.5438314748905</v>
+        <v>36.27557767191964</v>
       </c>
       <c r="D3" t="n">
-        <v>94.41467671741576</v>
+        <v>75.29514017720912</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.25285860600172</v>
+        <v>35.42931115085889</v>
       </c>
       <c r="C4" t="n">
-        <v>55.97729060074463</v>
+        <v>65.37065263497811</v>
       </c>
       <c r="D4" t="n">
-        <v>115.1963121209122</v>
+        <v>104.1820846269673</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.15596868291757</v>
+        <v>50.43728830567989</v>
       </c>
       <c r="C5" t="n">
-        <v>96.97212948697872</v>
+        <v>91.2779928023472</v>
       </c>
       <c r="D5" t="n">
-        <v>78.78525326580655</v>
+        <v>83.12948685709868</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.40515267334701</v>
+        <v>49.91205328390785</v>
       </c>
       <c r="C6" t="n">
-        <v>92.45805354285189</v>
+        <v>113.4694179091421</v>
       </c>
       <c r="D6" t="n">
-        <v>52.1258943569844</v>
+        <v>56.83533809425636</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.45393695892307</v>
+        <v>37.36924461445059</v>
       </c>
       <c r="C7" t="n">
-        <v>74.97803566873739</v>
+        <v>106.7179389470368</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>43.23813239043802</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.53664044579129</v>
+        <v>22.36421270274234</v>
       </c>
       <c r="C8" t="n">
-        <v>58.74778262212912</v>
+        <v>73.68507394224434</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.97968639784708</v>
+        <v>11.20468654856884</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>43.70937128847648</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>29.74204670015712</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.921558902447882</v>
+        <v>7.914496900145328</v>
       </c>
       <c r="C21" t="n">
-        <v>105.9508503202404</v>
+        <v>105.8563960394438</v>
       </c>
       <c r="D21" t="n">
-        <v>9.901948628059852</v>
+        <v>9.89312112518166</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.79038901737669</v>
+        <v>7.748934629620075</v>
       </c>
       <c r="C2" t="n">
-        <v>10.99361079215578</v>
+        <v>16.59546319258808</v>
       </c>
       <c r="D2" t="n">
-        <v>27.98079131873834</v>
+        <v>24.90693925674158</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.89774367450487</v>
+        <v>21.08303194870025</v>
       </c>
       <c r="C3" t="n">
-        <v>25.9770442543706</v>
+        <v>45.59236338522187</v>
       </c>
       <c r="D3" t="n">
-        <v>91.4497986505904</v>
+        <v>76.51250733047516</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.88197895797468</v>
+        <v>34.33171721751096</v>
       </c>
       <c r="C4" t="n">
-        <v>49.4938287618987</v>
+        <v>77.34208414056373</v>
       </c>
       <c r="D4" t="n">
-        <v>130.5881526280937</v>
+        <v>114.0731927472539</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.78843518863076</v>
+        <v>51.41903600992671</v>
       </c>
       <c r="C5" t="n">
-        <v>99.77011044408214</v>
+        <v>103.6971012610694</v>
       </c>
       <c r="D5" t="n">
-        <v>98.29748888771192</v>
+        <v>98.59201319898595</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.85800040691205</v>
+        <v>57.7611261793611</v>
       </c>
       <c r="C6" t="n">
-        <v>119.4266629785118</v>
+        <v>128.0405173355733</v>
       </c>
       <c r="D6" t="n">
-        <v>61.98755004614362</v>
+        <v>66.93850371866029</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>56.17364014159399</v>
+        <v>47.13076203777662</v>
       </c>
       <c r="C7" t="n">
-        <v>101.9270101503123</v>
+        <v>131.750541909922</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>48.86747372658923</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.63391558396972</v>
+        <v>30.62561963397925</v>
       </c>
       <c r="C8" t="n">
-        <v>76.93956758182253</v>
+        <v>103.8100022470577</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>41.0566889916016</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.081248379741</v>
+        <v>16.08593613408398</v>
       </c>
       <c r="C9" t="n">
-        <v>56.46718270516377</v>
+        <v>65.45311944213483</v>
       </c>
       <c r="D9" t="n">
-        <v>37.38593432542277</v>
+        <v>37.82968428774233</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>42.27896488338889</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.686282702997524</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>29.74204670015712</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.098374890673503</v>
+        <v>8.088976042507502</v>
       </c>
       <c r="C21" t="n">
-        <v>114.3895453307632</v>
+        <v>114.2567866004185</v>
       </c>
       <c r="D21" t="n">
-        <v>11.13526547467607</v>
+        <v>11.12234205844782</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.778207134298231</v>
+        <v>7.070546965985528</v>
       </c>
       <c r="C2" t="n">
-        <v>7.210936887692822</v>
+        <v>11.0191362324662</v>
       </c>
       <c r="D2" t="n">
-        <v>22.86294053649972</v>
+        <v>20.31334174857075</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>33.99301425954581</v>
+        <v>24.89712177969911</v>
       </c>
       <c r="C3" t="n">
-        <v>40.15838984221578</v>
+        <v>66.7588438887831</v>
       </c>
       <c r="D3" t="n">
-        <v>100.3444328510665</v>
+        <v>84.56283850529901</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.71612034921921</v>
+        <v>24.69586350032851</v>
       </c>
       <c r="C4" t="n">
-        <v>78.31205087235958</v>
+        <v>95.56724852220151</v>
       </c>
       <c r="D4" t="n">
-        <v>121.3351805155675</v>
+        <v>110.4996311037955</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.65002445786519</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="C5" t="n">
-        <v>71.34851440613696</v>
+        <v>76.50268985343271</v>
       </c>
       <c r="D5" t="n">
-        <v>64.40264939859077</v>
+        <v>67.44606728175589</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.85793398698726</v>
+        <v>29.26295382048468</v>
       </c>
       <c r="C6" t="n">
-        <v>67.09951034215676</v>
+        <v>86.78257006460107</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.25407703341745</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C7" t="n">
-        <v>54.07760879302705</v>
+        <v>73.00177754008857</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>41.55738032076748</v>
+        <v>48.23326470964579</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>27.87181732356695</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>24.89024954576939</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.769731257858504</v>
+        <v>4.209734155810323</v>
       </c>
       <c r="C2" t="n">
-        <v>3.682535638629786</v>
+        <v>4.51211244871834</v>
       </c>
       <c r="D2" t="n">
-        <v>16.99797975132928</v>
+        <v>15.74134268989336</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34.96003574822892</v>
+        <v>25.38308689330128</v>
       </c>
       <c r="C3" t="n">
-        <v>34.46425315758428</v>
+        <v>55.40002295064751</v>
       </c>
       <c r="D3" t="n">
-        <v>97.37464604571989</v>
+        <v>82.81532759173969</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.96306310679967</v>
+        <v>34.86775146402972</v>
       </c>
       <c r="C4" t="n">
-        <v>92.46590752448584</v>
+        <v>134.6849857979157</v>
       </c>
       <c r="D4" t="n">
-        <v>140.2367690654314</v>
+        <v>126.0573869729947</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.26423866782519</v>
+        <v>36.05468443846411</v>
       </c>
       <c r="C5" t="n">
-        <v>107.5013736150258</v>
+        <v>123.8965602759475</v>
       </c>
       <c r="D5" t="n">
-        <v>86.98284659626741</v>
+        <v>84.77391426171209</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.2642386678252</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="C6" t="n">
-        <v>88.71464954655879</v>
+        <v>104.9360668638288</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>40.21140421824511</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.93657161431823</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="C7" t="n">
-        <v>72.22325161062085</v>
+        <v>95.33948305481626</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>54.07466354991431</v>
+        <v>64.17193868809275</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
         <v>26.27647730416588</v>
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.029894399483909</v>
+        <v>4.37663126553228</v>
       </c>
       <c r="C2" t="n">
-        <v>6.700428081484481</v>
+        <v>6.884014902178635</v>
       </c>
       <c r="D2" t="n">
-        <v>23.8986843644801</v>
+        <v>25.12783249019711</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.13059780686061</v>
+        <v>19.94911335029519</v>
       </c>
       <c r="C3" t="n">
-        <v>23.50304003966864</v>
+        <v>35.09257168830224</v>
       </c>
       <c r="D3" t="n">
-        <v>88.88743714250622</v>
+        <v>76.52232480751763</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>55.90071427981338</v>
+        <v>41.4277896238069</v>
       </c>
       <c r="C4" t="n">
-        <v>89.08378668335557</v>
+        <v>136.5483429405761</v>
       </c>
       <c r="D4" t="n">
-        <v>155.4882196509056</v>
+        <v>137.6459368739241</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.41336650787948</v>
+        <v>43.83503499462009</v>
       </c>
       <c r="C5" t="n">
-        <v>139.678154621715</v>
+        <v>186.1639084178015</v>
       </c>
       <c r="D5" t="n">
-        <v>114.1527143112979</v>
+        <v>107.9186163893307</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.07305990740432</v>
+        <v>42.2642386678252</v>
       </c>
       <c r="C6" t="n">
-        <v>129.8518418499087</v>
+        <v>150.1789280663388</v>
       </c>
       <c r="D6" t="n">
-        <v>53.85671555957153</v>
+        <v>54.82275530055039</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.55457394637499</v>
+        <v>28.62579956042849</v>
       </c>
       <c r="C7" t="n">
-        <v>99.83097880174539</v>
+        <v>123.0070968558999</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.43936530761284</v>
+        <v>13.85246010692249</v>
       </c>
       <c r="C8" t="n">
-        <v>74.18576527141022</v>
+        <v>92.96169011513048</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>51.58593311964863</v>
+        <v>56.24530772400399</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>38.57777603837842</v>
+        <v>37.86600895279948</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>29.50740899884213</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.523492510541802</v>
+        <v>2.608503650183775</v>
       </c>
       <c r="C2" t="n">
-        <v>3.025746424488669</v>
+        <v>3.150428382928014</v>
       </c>
       <c r="D2" t="n">
-        <v>16.53950357344601</v>
+        <v>17.30035804423729</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.12078032981814</v>
+        <v>19.69385894719102</v>
       </c>
       <c r="C3" t="n">
-        <v>26.23229865747478</v>
+        <v>33.73775985644163</v>
       </c>
       <c r="D3" t="n">
-        <v>90.17843537359077</v>
+        <v>80.18424374435824</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>61.6056501891916</v>
+        <v>45.69053815564656</v>
       </c>
       <c r="C4" t="n">
-        <v>86.11007288719199</v>
+        <v>132.8982049761865</v>
       </c>
       <c r="D4" t="n">
-        <v>165.4814295324339</v>
+        <v>147.80506211747</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.93507544946203</v>
+        <v>45.7248993252952</v>
       </c>
       <c r="C5" t="n">
-        <v>167.2652651110504</v>
+        <v>227.9372732335032</v>
       </c>
       <c r="D5" t="n">
-        <v>124.26471566504</v>
+        <v>113.7845589222053</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.7070068824405</v>
+        <v>34.93843729873549</v>
       </c>
       <c r="C6" t="n">
-        <v>157.2632195001838</v>
+        <v>183.306040850739</v>
       </c>
       <c r="D6" t="n">
-        <v>52.93092747446678</v>
+        <v>53.61520562432682</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.89936301254809</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="C7" t="n">
-        <v>103.4241753992887</v>
+        <v>126.420633623566</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>62.0022762617073</v>
+        <v>70.59747741238813</v>
       </c>
       <c r="D8" t="n">
         <v>32.29459073119883</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>28.84374755077128</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>21.14586380177204</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
         <v>6.138868394655306</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.489532251520663</v>
+        <v>3.227004703859266</v>
       </c>
       <c r="C2" t="n">
-        <v>8.306567325632262</v>
+        <v>7.311075153525997</v>
       </c>
       <c r="D2" t="n">
-        <v>14.40027532589222</v>
+        <v>23.65030219530566</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.55150553007523</v>
+        <v>14.51023106876786</v>
       </c>
       <c r="C3" t="n">
-        <v>18.62866268808323</v>
+        <v>22.81581664669588</v>
       </c>
       <c r="D3" t="n">
-        <v>83.75780538781663</v>
+        <v>76.42415003709296</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.68749510154258</v>
+        <v>41.92553570986004</v>
       </c>
       <c r="C4" t="n">
-        <v>76.37211740876788</v>
+        <v>108.878765644084</v>
       </c>
       <c r="D4" t="n">
-        <v>171.6968742480204</v>
+        <v>152.6293703361389</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>71.96210672129121</v>
+        <v>55.66509483079416</v>
       </c>
       <c r="C5" t="n">
-        <v>164.6145463095839</v>
+        <v>237.852925046396</v>
       </c>
       <c r="D5" t="n">
-        <v>150.2564861349744</v>
+        <v>134.8675908709056</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.35231822376692</v>
+        <v>45.72588107299945</v>
       </c>
       <c r="C6" t="n">
-        <v>207.8595509339517</v>
+        <v>263.8496042548516</v>
       </c>
       <c r="D6" t="n">
-        <v>74.46556336712058</v>
+        <v>70.76241102670161</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.13430381349934</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>159.1187226612103</v>
+        <v>187.6247490017207</v>
       </c>
       <c r="D7" t="n">
-        <v>39.94436884268997</v>
+        <v>41.08221443191203</v>
       </c>
     </row>
     <row r="8">
@@ -3041,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.093127163183205</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>93.71272710887928</v>
+        <v>110.1520924164921</v>
       </c>
       <c r="D8" t="n">
         <v>34.13045893814036</v>
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>47.8140584399324</v>
+        <v>50.69843319500952</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
         <v>21.91359050649305</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3131,7 +3131,7 @@
         <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.254493639578176</v>
+        <v>2.306125357275758</v>
       </c>
       <c r="C2" t="n">
-        <v>4.214642894331557</v>
+        <v>4.924446484502001</v>
       </c>
       <c r="D2" t="n">
-        <v>10.99950127838126</v>
+        <v>16.8350096324243</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.97089172623786</v>
+        <v>13.17014545247096</v>
       </c>
       <c r="C3" t="n">
-        <v>25.29472959991907</v>
+        <v>25.56961895710818</v>
       </c>
       <c r="D3" t="n">
-        <v>77.78877934599603</v>
+        <v>78.01949005649402</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.20403326269664</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="C4" t="n">
-        <v>65.17921183264998</v>
+        <v>89.76021085158163</v>
       </c>
       <c r="D4" t="n">
-        <v>174.3132318798382</v>
+        <v>155.1946770873358</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79.86517574047804</v>
+        <v>60.35294011857268</v>
       </c>
       <c r="C5" t="n">
-        <v>160.8593613408399</v>
+        <v>231.9133514357028</v>
       </c>
       <c r="D5" t="n">
-        <v>169.2778479047563</v>
+        <v>148.8084082712103</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.34102027740147</v>
+        <v>53.33344403320799</v>
       </c>
       <c r="C6" t="n">
-        <v>236.2369683252058</v>
+        <v>312.59435951841</v>
       </c>
       <c r="D6" t="n">
-        <v>89.88194756690825</v>
+        <v>84.97124555026569</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.41566449399068</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="C7" t="n">
-        <v>208.1658562176767</v>
+        <v>248.5893179400391</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>45.6934833987593</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>124.2548981879975</v>
+        <v>143.8653085803276</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.13184159647211</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>57.57655761096267</v>
+        <v>57.90937008270233</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
         <v>24.52209415667683</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
         <v>20.39482680802324</v>
@@ -3428,7 +3428,7 @@
         <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.255696371460675</v>
+        <v>2.961932823712627</v>
       </c>
       <c r="C2" t="n">
-        <v>8.572620953483149</v>
+        <v>6.294966279630549</v>
       </c>
       <c r="D2" t="n">
-        <v>11.72403108411541</v>
+        <v>15.83951746031804</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.5887708851076</v>
+        <v>10.61269268290802</v>
       </c>
       <c r="C3" t="n">
-        <v>20.86704745376596</v>
+        <v>22.65382827549515</v>
       </c>
       <c r="D3" t="n">
-        <v>70.51402885752715</v>
+        <v>73.7636137585841</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.07418052382881</v>
+        <v>31.61325782445154</v>
       </c>
       <c r="C4" t="n">
-        <v>64.08161789930206</v>
+        <v>78.27376271189394</v>
       </c>
       <c r="D4" t="n">
-        <v>171.3522808038298</v>
+        <v>157.3388140734108</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79.52156404399165</v>
+        <v>59.29756133650736</v>
       </c>
       <c r="C5" t="n">
-        <v>142.5006792714246</v>
+        <v>201.5037162966579</v>
       </c>
       <c r="D5" t="n">
-        <v>188.0046853632642</v>
+        <v>164.3936530761284</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>82.8781594448115</v>
+        <v>62.91333813124836</v>
       </c>
       <c r="C6" t="n">
-        <v>245.2533392410085</v>
+        <v>339.0396974277063</v>
       </c>
       <c r="D6" t="n">
-        <v>113.9121861237574</v>
+        <v>103.7285171876053</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.81892612072463</v>
+        <v>32.75797564760332</v>
       </c>
       <c r="C7" t="n">
-        <v>266.2558678779604</v>
+        <v>326.9808903764426</v>
       </c>
       <c r="D7" t="n">
-        <v>56.11375353163493</v>
+        <v>54.67647489261761</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>184.2544091330414</v>
+        <v>213.2110576698011</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>94.96249193638545</v>
+        <v>101.5078038805989</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>45.55309347705201</v>
+        <v>44.55661955724149</v>
       </c>
       <c r="D10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.76244241776806</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
         <v>20.82875929330033</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.44517367838031</v>
+        <v>4.919537745980767</v>
       </c>
       <c r="C2" t="n">
-        <v>3.604977569994288</v>
+        <v>2.280599916965341</v>
       </c>
       <c r="D2" t="n">
-        <v>5.711808143307943</v>
+        <v>7.181484456565418</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.426700398448868</v>
+        <v>2.145118733779281</v>
       </c>
       <c r="C2" t="n">
-        <v>4.799764526062656</v>
+        <v>3.62559427178347</v>
       </c>
       <c r="D2" t="n">
-        <v>8.629562320329464</v>
+        <v>11.78391769407446</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.5136182802371</v>
+        <v>14.16171063376024</v>
       </c>
       <c r="C3" t="n">
-        <v>27.91108723173682</v>
+        <v>26.62008900065226</v>
       </c>
       <c r="D3" t="n">
-        <v>75.8694625841935</v>
+        <v>79.31048828757858</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>60.16346281165303</v>
+        <v>44.61846966260904</v>
       </c>
       <c r="C4" t="n">
-        <v>89.81126173220245</v>
+        <v>113.9838537061674</v>
       </c>
       <c r="D4" t="n">
-        <v>175.5001648542726</v>
+        <v>160.9761893176453</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.62734644967627</v>
+        <v>36.52101459798135</v>
       </c>
       <c r="C5" t="n">
-        <v>210.167639786636</v>
+        <v>293.6898257254334</v>
       </c>
       <c r="D5" t="n">
-        <v>171.1922559280376</v>
+        <v>149.3483695085461</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.56609287691869</v>
+        <v>20.32708621643021</v>
       </c>
       <c r="C6" t="n">
-        <v>225.852041109683</v>
+        <v>278.501206993031</v>
       </c>
       <c r="D6" t="n">
-        <v>87.58760318208346</v>
+        <v>82.15362963907737</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>129.5347373414369</v>
+        <v>149.8961847275158</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>69.9298889735003</v>
+        <v>74.76990515543707</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>24.78422079371073</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>34.72343455150543</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>20.96718571959912</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.20360698987336</v>
+        <v>22.34948648717864</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
         <v>16.70345544005523</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.624833508257476</v>
+        <v>5.748132808365075</v>
       </c>
       <c r="C2" t="n">
-        <v>2.287472150895068</v>
+        <v>4.550400609183966</v>
       </c>
       <c r="D2" t="n">
-        <v>12.52906420159779</v>
+        <v>11.93216159741573</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.69047173572177</v>
+        <v>10.45561305022853</v>
       </c>
       <c r="C3" t="n">
-        <v>9.228428419920018</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="D3" t="n">
-        <v>8.163232160812228</v>
+        <v>9.454230391896784</v>
       </c>
     </row>
     <row r="4">
@@ -4666,7 +4666,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
         <v>24.19517217116264</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39929799056473</v>
+        <v>13.39953577765612</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14926595060361</v>
+        <v>70.15051083596438</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576387998889969</v>
+        <v>1.576415973841896</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.641703145678919</v>
+        <v>4.742823159216341</v>
       </c>
       <c r="C2" t="n">
-        <v>3.076797305109504</v>
+        <v>6.10352547730242</v>
       </c>
       <c r="D2" t="n">
-        <v>13.48234122242145</v>
+        <v>28.5943836338926</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.22752878767378</v>
+        <v>16.31664684458199</v>
       </c>
       <c r="C3" t="n">
-        <v>9.036987617591889</v>
+        <v>13.41067364001143</v>
       </c>
       <c r="D3" t="n">
-        <v>16.71425466480195</v>
+        <v>17.19040230136165</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.88958659323463</v>
+        <v>12.23944862884498</v>
       </c>
       <c r="C4" t="n">
-        <v>14.83028082035232</v>
+        <v>9.584802836561609</v>
       </c>
       <c r="D4" t="n">
-        <v>19.34828375529614</v>
+        <v>20.02470792352219</v>
       </c>
     </row>
     <row r="5">
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.36836067773758</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.84843530511426</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5008,7 +5008,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44569776264674</v>
+        <v>15.44689212071116</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17073488634499</v>
+        <v>86.1773981471254</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251725844767735</v>
+        <v>3.25197728857077</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.396086293167969</v>
+        <v>4.739877916103601</v>
       </c>
       <c r="C2" t="n">
-        <v>3.163191103083223</v>
+        <v>4.600469742100554</v>
       </c>
       <c r="D2" t="n">
-        <v>24.12055934563989</v>
+        <v>23.18495378349267</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.47020039707199</v>
+        <v>16.57190124768616</v>
       </c>
       <c r="C3" t="n">
-        <v>10.85322087044849</v>
+        <v>19.67913273162732</v>
       </c>
       <c r="D3" t="n">
-        <v>23.62084976417826</v>
+        <v>36.07431939254905</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.33323874456295</v>
+        <v>23.12604892123787</v>
       </c>
       <c r="C4" t="n">
-        <v>19.50143639715864</v>
+        <v>23.61103228713579</v>
       </c>
       <c r="D4" t="n">
-        <v>23.20262524216912</v>
+        <v>23.95562573132642</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.98990478551705</v>
+        <v>11.1428364432013</v>
       </c>
       <c r="C5" t="n">
-        <v>18.13778883595982</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D5" t="n">
-        <v>29.77149913128453</v>
+        <v>30.01693605734623</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
         <v>12.19625172985813</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>37.42913122440964</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
         <v>38.55323234577224</v>
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5277,7 +5277,7 @@
         <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>45.77987719673301</v>
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
         <v>43.35888735806038</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74713043816062</v>
+        <v>16.74612725184558</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1574956727798</v>
+        <v>102.1513762362581</v>
       </c>
       <c r="D21" t="n">
-        <v>5.024139131448187</v>
+        <v>5.023838175553675</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.252751128347935</v>
+        <v>4.811545498513618</v>
       </c>
       <c r="C2" t="n">
-        <v>4.73104218676538</v>
+        <v>6.12512392679585</v>
       </c>
       <c r="D2" t="n">
-        <v>22.66659099565036</v>
+        <v>23.61790452106552</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.01783568959246</v>
+        <v>16.58171872472863</v>
       </c>
       <c r="C3" t="n">
-        <v>11.68770641905828</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D3" t="n">
-        <v>36.69772918474577</v>
+        <v>45.67090320156162</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.60049510429634</v>
+        <v>27.88654353913065</v>
       </c>
       <c r="C4" t="n">
-        <v>23.85352397008475</v>
+        <v>38.18605870438394</v>
       </c>
       <c r="D4" t="n">
-        <v>29.23939187558275</v>
+        <v>35.7356164345839</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.44613973055134</v>
+        <v>23.07107104980005</v>
       </c>
       <c r="C5" t="n">
-        <v>27.80800372279091</v>
+        <v>29.50151851261666</v>
       </c>
       <c r="D5" t="n">
-        <v>31.56318869153496</v>
+        <v>32.0295188510522</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.63901994447344</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>21.1321193339126</v>
+        <v>16.38242394076653</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>37.91705983342032</v>
       </c>
     </row>
     <row r="7">
@@ -5518,7 +5518,7 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
         <v>40.00425545264903</v>
@@ -5529,7 +5529,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
         <v>31.46010518258904</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.60155896745857</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>50.46575898910303</v>
@@ -5588,7 +5588,7 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
         <v>47.29864089520282</v>
@@ -5599,7 +5599,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>33.30088212805181</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>44.07556318216055</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>30.58536797810513</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08518927328956</v>
+        <v>18.08200707616574</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9843300209843</v>
+        <v>117.9635699730813</v>
       </c>
       <c r="D21" t="n">
-        <v>6.889595913634118</v>
+        <v>6.88838364806314</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.803511590430396</v>
+        <v>7.043058030266617</v>
       </c>
       <c r="C2" t="n">
-        <v>8.620726590991241</v>
+        <v>5.656830271870121</v>
       </c>
       <c r="D2" t="n">
-        <v>35.35568007304038</v>
+        <v>22.41526358336318</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.73174619702914</v>
+        <v>14.78021168743573</v>
       </c>
       <c r="C3" t="n">
-        <v>14.75566799482956</v>
+        <v>20.35653864755761</v>
       </c>
       <c r="D3" t="n">
-        <v>43.62395923820702</v>
+        <v>50.29493488856409</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.30396623988479</v>
+        <v>22.02845498788993</v>
       </c>
       <c r="C4" t="n">
-        <v>22.64106555533994</v>
+        <v>35.72285371442869</v>
       </c>
       <c r="D4" t="n">
-        <v>35.8887690764464</v>
+        <v>43.16351956491527</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.48831382410494</v>
+        <v>20.2240027074843</v>
       </c>
       <c r="C5" t="n">
-        <v>27.43984833369836</v>
+        <v>38.9508401659922</v>
       </c>
       <c r="D5" t="n">
-        <v>28.44613973055134</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.32958949118645</v>
+        <v>11.55222523587222</v>
       </c>
       <c r="C6" t="n">
-        <v>22.58117894538089</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="D6" t="n">
-        <v>30.30949687321178</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.928774385946488</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>16.88802400845363</v>
+        <v>14.43267300013236</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -5840,10 +5840,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
         <v>30.12492830481337</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.32797015314322</v>
@@ -5910,7 +5910,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
         <v>19.25207248027995</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -5986,7 +5986,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.074682935400947</v>
+        <v>7.071900272680289</v>
       </c>
       <c r="C21" t="n">
-        <v>67.20948788630899</v>
+        <v>67.18305259046275</v>
       </c>
       <c r="D21" t="n">
-        <v>5.30601220155071</v>
+        <v>5.303925204510217</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.222316949516284</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C2" t="n">
-        <v>7.123561342014856</v>
+        <v>5.65093978564464</v>
       </c>
       <c r="D2" t="n">
-        <v>35.20056393576939</v>
+        <v>25.9161758967073</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.03532722181966</v>
+        <v>21.00449213236051</v>
       </c>
       <c r="C3" t="n">
-        <v>27.37112599440108</v>
+        <v>21.54445336969626</v>
       </c>
       <c r="D3" t="n">
-        <v>63.77433086787281</v>
+        <v>57.38315331322607</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.92781800043802</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="C4" t="n">
-        <v>31.97061398879738</v>
+        <v>45.70330087580177</v>
       </c>
       <c r="D4" t="n">
-        <v>51.16574510223102</v>
+        <v>60.34214089382595</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>27.90617849321559</v>
       </c>
       <c r="C5" t="n">
-        <v>36.59464567579986</v>
+        <v>56.13142499031139</v>
       </c>
       <c r="D5" t="n">
-        <v>35.46563581591603</v>
+        <v>39.93258787023902</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.87552333020568</v>
+        <v>21.05161602216436</v>
       </c>
       <c r="C6" t="n">
-        <v>35.42145716922493</v>
+        <v>46.249152599363</v>
       </c>
       <c r="D6" t="n">
-        <v>33.16736444027425</v>
+        <v>33.97239755775664</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.45641487148353</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>26.35010838198439</v>
+        <v>25.03260296288517</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>21.27938148954961</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D8" t="n">
         <v>32.04424506661589</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>21.33337761328319</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -6266,7 +6266,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.305152462060006</v>
+        <v>7.301089542085998</v>
       </c>
       <c r="C21" t="n">
-        <v>77.61724490938757</v>
+        <v>77.57407638466373</v>
       </c>
       <c r="D21" t="n">
-        <v>6.392008404302505</v>
+        <v>6.388453349325248</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.343472827766142</v>
+        <v>4.301036692305276</v>
       </c>
       <c r="C2" t="n">
-        <v>3.945644023367931</v>
+        <v>9.709484795000956</v>
       </c>
       <c r="D2" t="n">
-        <v>39.48294742169397</v>
+        <v>27.45162930614931</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.88806506618264</v>
+        <v>20.86213871524472</v>
       </c>
       <c r="C3" t="n">
-        <v>27.62638039750524</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D3" t="n">
-        <v>77.9311327631118</v>
+        <v>65.28622233241289</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.19431359664541</v>
+        <v>35.31444666946201</v>
       </c>
       <c r="C4" t="n">
-        <v>54.25432337979149</v>
+        <v>50.78286349757476</v>
       </c>
       <c r="D4" t="n">
-        <v>72.72197944437823</v>
+        <v>76.4104055692335</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.48513190128072</v>
+        <v>34.82749980815561</v>
       </c>
       <c r="C5" t="n">
-        <v>49.57825906446394</v>
+        <v>72.94385442553802</v>
       </c>
       <c r="D5" t="n">
-        <v>46.4612101034803</v>
+        <v>53.30890034060182</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.70951015719674</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>48.66425195181016</v>
+        <v>70.76241102670161</v>
       </c>
       <c r="D6" t="n">
-        <v>36.91076843656734</v>
+        <v>38.88309957439917</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.0382724649324</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="C7" t="n">
-        <v>40.78278138211675</v>
+        <v>48.32849423695774</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>29.37389131106456</v>
+        <v>27.53802310412303</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>24.51718541815559</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
         <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>22.12466626290612</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>18.18589447346791</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.52449537157027</v>
+        <v>7.51923743108413</v>
       </c>
       <c r="C21" t="n">
-        <v>87.47225869450439</v>
+        <v>87.411135136353</v>
       </c>
       <c r="D21" t="n">
-        <v>7.52449537157027</v>
+        <v>7.51923743108413</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_14_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497625627163</v>
+        <v>10.84497639106456</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907167728637</v>
+        <v>37.78907214696923</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.191481860057134</v>
+        <v>1.130973355292326</v>
       </c>
       <c r="C2" t="n">
-        <v>10.54004335279376</v>
+        <v>2.738094347144354</v>
       </c>
       <c r="D2" t="n">
-        <v>26.26371458401067</v>
+        <v>10.36529226143782</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.50456156672063</v>
+        <v>9.189158511750145</v>
       </c>
       <c r="C3" t="n">
-        <v>31.15576339427253</v>
+        <v>33.43832680664636</v>
       </c>
       <c r="D3" t="n">
-        <v>71.62831250184728</v>
+        <v>59.78843518863076</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.95632974159018</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C4" t="n">
-        <v>53.02910224489146</v>
+        <v>110.6144955851924</v>
       </c>
       <c r="D4" t="n">
-        <v>90.37282141903162</v>
+        <v>78.14613551034185</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.62043315801754</v>
+        <v>14.03899217072939</v>
       </c>
       <c r="C5" t="n">
-        <v>84.45484625783187</v>
+        <v>139.1381933843792</v>
       </c>
       <c r="D5" t="n">
-        <v>68.74688298988291</v>
+        <v>48.74377351585415</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.40637110076273</v>
+        <v>9.821404033285093</v>
       </c>
       <c r="C6" t="n">
-        <v>94.83290123942491</v>
+        <v>99.38133835320039</v>
       </c>
       <c r="D6" t="n">
-        <v>46.73217246985243</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.38625312059227</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>76.29554108783661</v>
+        <v>53.89794896314989</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.68694565553228</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>46.98153638673111</v>
+        <v>30.45872252425729</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17499743772996</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.724119341972541</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.55149177465677</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.689634259719108</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.544731107136738</v>
+        <v>1.001382658331747</v>
       </c>
       <c r="C2" t="n">
-        <v>14.31584502332699</v>
+        <v>9.835148501144547</v>
       </c>
       <c r="D2" t="n">
-        <v>24.68113728476482</v>
+        <v>14.32369900496096</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.63709750679395</v>
+        <v>6.351907646476864</v>
       </c>
       <c r="C3" t="n">
-        <v>36.27557767191964</v>
+        <v>20.36635612460008</v>
       </c>
       <c r="D3" t="n">
-        <v>75.29514017720912</v>
+        <v>54.36427912266712</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.42931115085889</v>
+        <v>16.73192612347839</v>
       </c>
       <c r="C4" t="n">
-        <v>65.37065263497811</v>
+        <v>95.58001124235672</v>
       </c>
       <c r="D4" t="n">
-        <v>104.1820846269673</v>
+        <v>89.86231261282329</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.43728830567989</v>
+        <v>18.60411899547706</v>
       </c>
       <c r="C5" t="n">
-        <v>91.2779928023472</v>
+        <v>175.7082953675729</v>
       </c>
       <c r="D5" t="n">
-        <v>83.12948685709868</v>
+        <v>64.79534848028949</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.91205328390785</v>
+        <v>14.08807955594173</v>
       </c>
       <c r="C6" t="n">
-        <v>113.4694179091421</v>
+        <v>162.3349281403229</v>
       </c>
       <c r="D6" t="n">
-        <v>56.83533809425636</v>
+        <v>37.79630486579796</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.36924461445059</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>106.7179389470368</v>
+        <v>98.57335999260523</v>
       </c>
       <c r="D7" t="n">
-        <v>43.23813239043802</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.36421270274234</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>73.68507394224434</v>
+        <v>50.40292713603124</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.20468654856884</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>43.70937128847648</v>
+        <v>35.49999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.914496900145328</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.8563960394438</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.89312112518166</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.748934629620075</v>
+        <v>0.5379977419272521</v>
       </c>
       <c r="C2" t="n">
-        <v>16.59546319258808</v>
+        <v>4.112541133089889</v>
       </c>
       <c r="D2" t="n">
-        <v>24.90693925674158</v>
+        <v>9.809623060834129</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.08303194870025</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C3" t="n">
-        <v>45.59236338522187</v>
+        <v>30.61089341841555</v>
       </c>
       <c r="D3" t="n">
-        <v>76.51250733047516</v>
+        <v>55.04168503859743</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.33171721751096</v>
+        <v>18.21240166148258</v>
       </c>
       <c r="C4" t="n">
-        <v>77.34208414056373</v>
+        <v>87.30976858178158</v>
       </c>
       <c r="D4" t="n">
-        <v>114.0731927472539</v>
+        <v>96.86904597803279</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.41903600992671</v>
+        <v>18.55503161026472</v>
       </c>
       <c r="C5" t="n">
-        <v>103.6971012610694</v>
+        <v>200.4237938219864</v>
       </c>
       <c r="D5" t="n">
-        <v>98.59201319898595</v>
+        <v>72.52661165123313</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.7611261793611</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>128.0405173355733</v>
+        <v>203.3111138201762</v>
       </c>
       <c r="D6" t="n">
-        <v>66.93850371866029</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.13076203777662</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>131.750541909922</v>
+        <v>92.58469899669969</v>
       </c>
       <c r="D7" t="n">
-        <v>48.86747372658923</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.62561963397925</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>103.8100022470577</v>
+        <v>43.39324852770901</v>
       </c>
       <c r="D8" t="n">
-        <v>41.0566889916016</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.08593613408398</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>65.45311944213483</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>37.82968428774233</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.36157055926586</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.088976042507502</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.2567866004185</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.12234205844782</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.070546965985528</v>
+        <v>0.6047565858160352</v>
       </c>
       <c r="C2" t="n">
-        <v>11.0191362324662</v>
+        <v>8.834747590517047</v>
       </c>
       <c r="D2" t="n">
-        <v>20.31334174857075</v>
+        <v>14.73308779763188</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.89712177969911</v>
+        <v>3.760093707265284</v>
       </c>
       <c r="C3" t="n">
-        <v>66.7588438887831</v>
+        <v>22.5605622435917</v>
       </c>
       <c r="D3" t="n">
-        <v>84.56283850529901</v>
+        <v>50.38820092046754</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.69586350032851</v>
+        <v>14.94514530174919</v>
       </c>
       <c r="C4" t="n">
-        <v>95.56724852220151</v>
+        <v>82.31954500109505</v>
       </c>
       <c r="D4" t="n">
-        <v>110.4996311037955</v>
+        <v>101.9103204393402</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.5203927031756</v>
+        <v>22.776546738526</v>
       </c>
       <c r="C5" t="n">
-        <v>76.50268985343271</v>
+        <v>182.2369176008142</v>
       </c>
       <c r="D5" t="n">
-        <v>67.44606728175589</v>
+        <v>88.87271092694252</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.26295382048468</v>
+        <v>17.26796036999715</v>
       </c>
       <c r="C6" t="n">
-        <v>86.78257006460107</v>
+        <v>263.0043194814951</v>
       </c>
       <c r="D6" t="n">
-        <v>32.16107304342126</v>
+        <v>50.59633143376788</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>73.00177754008857</v>
+        <v>184.8699649436041</v>
       </c>
       <c r="D7" t="n">
-        <v>28.86534600026472</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>48.23326470964579</v>
+        <v>77.77405313043232</v>
       </c>
       <c r="D8" t="n">
-        <v>27.87181732356695</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>31.50624732468863</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>27.84531013555227</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>27.75891633757857</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.209734155810323</v>
+        <v>0.4025165587411922</v>
       </c>
       <c r="C2" t="n">
-        <v>4.51211244871834</v>
+        <v>4.143957059625786</v>
       </c>
       <c r="D2" t="n">
-        <v>15.74134268989336</v>
+        <v>10.44972256400305</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.38308689330128</v>
+        <v>3.05323536020758</v>
       </c>
       <c r="C3" t="n">
-        <v>55.40002295064751</v>
+        <v>29.1480893390878</v>
       </c>
       <c r="D3" t="n">
-        <v>82.81532759173969</v>
+        <v>51.13432917569511</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.86775146402972</v>
+        <v>12.25221134900019</v>
       </c>
       <c r="C4" t="n">
-        <v>134.6849857979157</v>
+        <v>72.30080967925635</v>
       </c>
       <c r="D4" t="n">
-        <v>126.0573869729947</v>
+        <v>103.9778811044839</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.05468443846411</v>
+        <v>24.02827506144069</v>
       </c>
       <c r="C5" t="n">
-        <v>123.8965602759475</v>
+        <v>175.7819264453914</v>
       </c>
       <c r="D5" t="n">
-        <v>84.77391426171209</v>
+        <v>101.2427320004523</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.66296710446964</v>
+        <v>21.05161602216436</v>
       </c>
       <c r="C6" t="n">
-        <v>104.9360668638288</v>
+        <v>286.269776576736</v>
       </c>
       <c r="D6" t="n">
-        <v>40.21140421824511</v>
+        <v>60.09572222006002</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>95.33948305481626</v>
+        <v>256.1350307948801</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>40.54323494228053</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>64.17193868809275</v>
+        <v>120.8335074386974</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>49.25624581747095</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.37663126553228</v>
+        <v>0.6499169802113884</v>
       </c>
       <c r="C2" t="n">
-        <v>6.884014902178635</v>
+        <v>7.256097282088176</v>
       </c>
       <c r="D2" t="n">
-        <v>25.12783249019711</v>
+        <v>12.86973065497144</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.94911335029519</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C3" t="n">
-        <v>35.09257168830224</v>
+        <v>22.38875639534851</v>
       </c>
       <c r="D3" t="n">
-        <v>76.52232480751763</v>
+        <v>48.33634821859171</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.4277896238069</v>
+        <v>9.278497552836605</v>
       </c>
       <c r="C4" t="n">
-        <v>136.5483429405761</v>
+        <v>72.42843688080843</v>
       </c>
       <c r="D4" t="n">
-        <v>137.6459368739241</v>
+        <v>104.2586609478985</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.83503499462009</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="C5" t="n">
-        <v>186.1639084178015</v>
+        <v>157.2268948351267</v>
       </c>
       <c r="D5" t="n">
-        <v>107.9186163893307</v>
+        <v>113.3182287626881</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.2642386678252</v>
+        <v>25.80131141531043</v>
       </c>
       <c r="C6" t="n">
-        <v>150.1789280663388</v>
+        <v>284.4584520624006</v>
       </c>
       <c r="D6" t="n">
-        <v>54.82275530055039</v>
+        <v>74.54606667886881</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.62579956042849</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="C7" t="n">
-        <v>123.0070968558999</v>
+        <v>328.41816901546</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>46.83132898798135</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>92.96169011513048</v>
+        <v>210.9579466885546</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87596529856218</v>
+        <v>41.22358610132356</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>56.24530772400399</v>
+        <v>90.52499231318986</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>37.86600895279948</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.03256190515617</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.608503650183775</v>
+        <v>0.4466952054322987</v>
       </c>
       <c r="C2" t="n">
-        <v>3.150428382928014</v>
+        <v>3.889684404225862</v>
       </c>
       <c r="D2" t="n">
-        <v>17.30035804423729</v>
+        <v>9.368818341627312</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.69385894719102</v>
+        <v>3.283946070705581</v>
       </c>
       <c r="C3" t="n">
-        <v>33.73775985644163</v>
+        <v>27.84236489243954</v>
       </c>
       <c r="D3" t="n">
-        <v>80.18424374435824</v>
+        <v>53.34326151025044</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.69053815564656</v>
+        <v>15.17487426454295</v>
       </c>
       <c r="C4" t="n">
-        <v>132.8982049761865</v>
+        <v>100.6723365842849</v>
       </c>
       <c r="D4" t="n">
-        <v>147.80506211747</v>
+        <v>107.0919848223548</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.7248993252952</v>
+        <v>15.75705065316131</v>
       </c>
       <c r="C5" t="n">
-        <v>227.9372732335032</v>
+        <v>236.3312161048135</v>
       </c>
       <c r="D5" t="n">
-        <v>113.7845589222053</v>
+        <v>105.5869655917445</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.93843729873549</v>
+        <v>9.016370915802709</v>
       </c>
       <c r="C6" t="n">
-        <v>183.306040850739</v>
+        <v>283.2106507303029</v>
       </c>
       <c r="D6" t="n">
-        <v>53.61520562432682</v>
+        <v>63.75862290460487</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.162651323735481</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C7" t="n">
-        <v>126.420633623566</v>
+        <v>148.3391328685803</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>35.39298648580176</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>70.59747741238813</v>
+        <v>66.67539533392211</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>28.84374755077128</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>26.07031028627404</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.227004703859266</v>
+        <v>0.2474004214701962</v>
       </c>
       <c r="C2" t="n">
-        <v>7.311075153525997</v>
+        <v>3.122939447209104</v>
       </c>
       <c r="D2" t="n">
-        <v>23.65030219530566</v>
+        <v>7.281622722398593</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.51023106876786</v>
+        <v>2.400373136883451</v>
       </c>
       <c r="C3" t="n">
-        <v>22.81581664669588</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D3" t="n">
-        <v>76.42415003709296</v>
+        <v>48.58178514465342</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.92553570986004</v>
+        <v>10.1718879637012</v>
       </c>
       <c r="C4" t="n">
-        <v>108.878765644084</v>
+        <v>81.31129010883357</v>
       </c>
       <c r="D4" t="n">
-        <v>152.6293703361389</v>
+        <v>105.7136110455923</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.66509483079416</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="C5" t="n">
-        <v>237.852925046396</v>
+        <v>191.9807635654638</v>
       </c>
       <c r="D5" t="n">
-        <v>134.8675908709056</v>
+        <v>106.1514705216864</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.72588107299945</v>
+        <v>8.93586760405447</v>
       </c>
       <c r="C6" t="n">
-        <v>263.8496042548516</v>
+        <v>268.398041368627</v>
       </c>
       <c r="D6" t="n">
-        <v>70.76241102670161</v>
+        <v>66.65674212754145</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.64280806657018</v>
+        <v>3.173990327829938</v>
       </c>
       <c r="C7" t="n">
-        <v>187.6247490017207</v>
+        <v>189.1818008606561</v>
       </c>
       <c r="D7" t="n">
-        <v>41.08221443191203</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>110.1520924164921</v>
+        <v>77.52370746584938</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>50.69843319500952</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>17.65182372235765</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.306125357275758</v>
+        <v>0.2660536278508856</v>
       </c>
       <c r="C2" t="n">
-        <v>4.924446484502001</v>
+        <v>7.120616098902116</v>
       </c>
       <c r="D2" t="n">
-        <v>16.8350096324243</v>
+        <v>8.685521939471531</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.17014545247096</v>
+        <v>1.546252634188726</v>
       </c>
       <c r="C3" t="n">
-        <v>25.56961895710818</v>
+        <v>15.89449533175586</v>
       </c>
       <c r="D3" t="n">
-        <v>78.01949005649402</v>
+        <v>43.30979997284804</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.49687181600267</v>
+        <v>7.351326809400116</v>
       </c>
       <c r="C4" t="n">
-        <v>89.76021085158163</v>
+        <v>65.37065263497811</v>
       </c>
       <c r="D4" t="n">
-        <v>155.1946770873358</v>
+        <v>106.249645292111</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.35294011857268</v>
+        <v>15.53615741970578</v>
       </c>
       <c r="C5" t="n">
-        <v>231.9133514357028</v>
+        <v>171.0204500797944</v>
       </c>
       <c r="D5" t="n">
-        <v>148.8084082712103</v>
+        <v>119.6995888402924</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.33344403320799</v>
+        <v>14.4503444588088</v>
       </c>
       <c r="C6" t="n">
-        <v>312.59435951841</v>
+        <v>288.6848759291831</v>
       </c>
       <c r="D6" t="n">
-        <v>84.97124555026569</v>
+        <v>83.28067600355268</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>248.5893179400391</v>
+        <v>293.9234816790441</v>
       </c>
       <c r="D7" t="n">
-        <v>45.6934833987593</v>
+        <v>44.0765449298648</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>143.8653085803276</v>
+        <v>163.8929617469625</v>
       </c>
       <c r="D8" t="n">
-        <v>35.13184159647211</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>57.90937008270233</v>
+        <v>62.23593221531803</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>22.2984356065578</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>16.70345544005523</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.961932823712627</v>
+        <v>0.3612831551628262</v>
       </c>
       <c r="C2" t="n">
-        <v>6.294966279630549</v>
+        <v>9.090983741325465</v>
       </c>
       <c r="D2" t="n">
-        <v>15.83951746031804</v>
+        <v>10.6352728801057</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.61269268290802</v>
+        <v>1.207549676223577</v>
       </c>
       <c r="C3" t="n">
-        <v>22.65382827549515</v>
+        <v>22.13350199224434</v>
       </c>
       <c r="D3" t="n">
-        <v>73.7636137585841</v>
+        <v>40.34492190602268</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.61325782445154</v>
+        <v>5.156138942704248</v>
       </c>
       <c r="C4" t="n">
-        <v>78.27376271189394</v>
+        <v>51.99532191231957</v>
       </c>
       <c r="D4" t="n">
-        <v>157.3388140734108</v>
+        <v>104.105508306036</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.29756133650736</v>
+        <v>13.54811831860599</v>
       </c>
       <c r="C5" t="n">
-        <v>201.5037162966579</v>
+        <v>145.6913593102267</v>
       </c>
       <c r="D5" t="n">
-        <v>164.3936530761284</v>
+        <v>129.8606775792469</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.91333813124836</v>
+        <v>17.67047692873834</v>
       </c>
       <c r="C6" t="n">
-        <v>339.0396974277063</v>
+        <v>282.0031010540794</v>
       </c>
       <c r="D6" t="n">
-        <v>103.7285171876053</v>
+        <v>98.69706020334036</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.75797564760332</v>
+        <v>11.37845589222053</v>
       </c>
       <c r="C7" t="n">
-        <v>326.9808903764426</v>
+        <v>352.0134933393278</v>
       </c>
       <c r="D7" t="n">
-        <v>54.67647489261761</v>
+        <v>56.11375353163493</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>213.2110576698011</v>
+        <v>272.1257374016521</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>101.5078038805989</v>
+        <v>127.6890516574529</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>24.18437294641592</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>47.97310156802039</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.919537745980767</v>
+        <v>3.493058331710151</v>
       </c>
       <c r="C2" t="n">
-        <v>2.280599916965341</v>
+        <v>15.25439582858694</v>
       </c>
       <c r="D2" t="n">
-        <v>7.181484456565418</v>
+        <v>12.97870465014283</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.145118733779281</v>
+        <v>0.3259402378099411</v>
       </c>
       <c r="C2" t="n">
-        <v>3.62559427178347</v>
+        <v>12.69596131131975</v>
       </c>
       <c r="D2" t="n">
-        <v>11.78391769407446</v>
+        <v>15.45369061254904</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.16171063376024</v>
+        <v>1.187914722138641</v>
       </c>
       <c r="C3" t="n">
-        <v>26.62008900065226</v>
+        <v>28.34796496012665</v>
       </c>
       <c r="D3" t="n">
-        <v>79.31048828757858</v>
+        <v>39.33863050916969</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.61846966260904</v>
+        <v>3.803290606252144</v>
       </c>
       <c r="C4" t="n">
-        <v>113.9838537061674</v>
+        <v>53.41198384954772</v>
       </c>
       <c r="D4" t="n">
-        <v>160.9761893176453</v>
+        <v>101.0552181889412</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.52101459798135</v>
+        <v>11.11829275059513</v>
       </c>
       <c r="C5" t="n">
-        <v>293.6898257254334</v>
+        <v>121.515822093149</v>
       </c>
       <c r="D5" t="n">
-        <v>149.3483695085461</v>
+        <v>134.7939597930871</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.32708621643021</v>
+        <v>17.99249017573129</v>
       </c>
       <c r="C6" t="n">
-        <v>278.501206993031</v>
+        <v>261.1929949671597</v>
       </c>
       <c r="D6" t="n">
-        <v>82.15362963907737</v>
+        <v>113.8316828120092</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>15.51063197939536</v>
       </c>
       <c r="C7" t="n">
-        <v>149.8961847275158</v>
+        <v>376.2076837627862</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>67.43232281389642</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>74.76990515543707</v>
+        <v>359.7467200056799</v>
       </c>
       <c r="D8" t="n">
-        <v>24.78422079371073</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>216.9937315742639</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>89.39794594871455</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>35.89465956267188</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.86995163914969</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.748132808365075</v>
+        <v>4.236241343824987</v>
       </c>
       <c r="C2" t="n">
-        <v>4.550400609183966</v>
+        <v>9.906816083554563</v>
       </c>
       <c r="D2" t="n">
-        <v>11.93216159741573</v>
+        <v>21.81836097918111</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.45561305022853</v>
+        <v>5.640140560897926</v>
       </c>
       <c r="C3" t="n">
-        <v>5.836490101747287</v>
+        <v>30.12001956629214</v>
       </c>
       <c r="D3" t="n">
-        <v>9.454230391896784</v>
+        <v>11.8644210058227</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39953577765612</v>
+        <v>11.67713319683914</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15051083596438</v>
+        <v>59.9426170771076</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576415973841896</v>
+        <v>0.7784755464559429</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.742823159216341</v>
+        <v>2.319869825135213</v>
       </c>
       <c r="C2" t="n">
-        <v>6.10352547730242</v>
+        <v>5.882632243846888</v>
       </c>
       <c r="D2" t="n">
-        <v>28.5943836338926</v>
+        <v>20.64419072490193</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.31664684458199</v>
+        <v>11.3588209381356</v>
       </c>
       <c r="C3" t="n">
-        <v>13.41067364001143</v>
+        <v>35.76997760423254</v>
       </c>
       <c r="D3" t="n">
-        <v>17.19040230136165</v>
+        <v>28.08289307998001</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.23944862884498</v>
+        <v>7.121597846606362</v>
       </c>
       <c r="C4" t="n">
-        <v>9.584802836561609</v>
+        <v>48.72806555258618</v>
       </c>
       <c r="D4" t="n">
-        <v>20.02470792352219</v>
+        <v>20.50969128942011</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44689212071116</v>
+        <v>13.62507828289498</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1773981471254</v>
+        <v>73.73571776625518</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25197728857077</v>
+        <v>1.602950386222939</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.739877916103601</v>
+        <v>2.217768063893545</v>
       </c>
       <c r="C2" t="n">
-        <v>4.600469742100554</v>
+        <v>5.821763886183585</v>
       </c>
       <c r="D2" t="n">
-        <v>23.18495378349267</v>
+        <v>24.06656322190631</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.57190124768616</v>
+        <v>9.47386534598172</v>
       </c>
       <c r="C3" t="n">
-        <v>19.67913273162732</v>
+        <v>27.63619787454772</v>
       </c>
       <c r="D3" t="n">
-        <v>36.07431939254905</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.12604892123787</v>
+        <v>15.86406115292421</v>
       </c>
       <c r="C4" t="n">
-        <v>23.61103228713579</v>
+        <v>74.06206506067512</v>
       </c>
       <c r="D4" t="n">
-        <v>23.95562573132642</v>
+        <v>30.46461301048277</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.1428364432013</v>
+        <v>6.994952392758526</v>
       </c>
       <c r="C5" t="n">
-        <v>12.541826921753</v>
+        <v>56.03325021988672</v>
       </c>
       <c r="D5" t="n">
-        <v>30.01693605734623</v>
+        <v>27.3171298706675</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74612725184558</v>
+        <v>14.83026545281883</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1513762362581</v>
+        <v>87.33378544437757</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023838175553675</v>
+        <v>2.471710908803139</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.811545498513618</v>
+        <v>1.645409152317654</v>
       </c>
       <c r="C2" t="n">
-        <v>6.12512392679585</v>
+        <v>9.091965489029711</v>
       </c>
       <c r="D2" t="n">
-        <v>23.61790452106552</v>
+        <v>19.21280257211008</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.58171872472863</v>
+        <v>8.462665210607506</v>
       </c>
       <c r="C3" t="n">
-        <v>18.60902773399829</v>
+        <v>24.64677611511618</v>
       </c>
       <c r="D3" t="n">
-        <v>45.67090320156162</v>
+        <v>48.92539684113979</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.88654353913065</v>
+        <v>17.44663845217007</v>
       </c>
       <c r="C4" t="n">
-        <v>38.18605870438394</v>
+        <v>70.57784245830319</v>
       </c>
       <c r="D4" t="n">
-        <v>35.7356164345839</v>
+        <v>42.97207876258713</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.07107104980005</v>
+        <v>15.75705065316131</v>
       </c>
       <c r="C5" t="n">
-        <v>29.50151851261666</v>
+        <v>102.1263049342745</v>
       </c>
       <c r="D5" t="n">
-        <v>32.0295188510522</v>
+        <v>32.17678100668922</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.6666888066416</v>
+        <v>7.084291433844984</v>
       </c>
       <c r="C6" t="n">
-        <v>16.38242394076653</v>
+        <v>53.3736956890821</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>33.40887437551896</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.58536797810513</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08200707616574</v>
+        <v>16.06404822351143</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9635699730813</v>
+        <v>100.6116704525189</v>
       </c>
       <c r="D21" t="n">
-        <v>6.88838364806314</v>
+        <v>3.381904889160301</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.043058030266617</v>
+        <v>2.381719930502762</v>
       </c>
       <c r="C2" t="n">
-        <v>5.656830271870121</v>
+        <v>6.473644361803467</v>
       </c>
       <c r="D2" t="n">
-        <v>22.41526358336318</v>
+        <v>19.30705035171777</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.78021168743573</v>
+        <v>6.916412576418779</v>
       </c>
       <c r="C3" t="n">
-        <v>20.35653864755761</v>
+        <v>30.64525458806419</v>
       </c>
       <c r="D3" t="n">
-        <v>50.29493488856409</v>
+        <v>52.64131190171398</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.02845498788993</v>
+        <v>16.93612964596173</v>
       </c>
       <c r="C4" t="n">
-        <v>35.72285371442869</v>
+        <v>65.67695791870312</v>
       </c>
       <c r="D4" t="n">
-        <v>43.16351956491527</v>
+        <v>57.02383365347173</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.2240027074843</v>
+        <v>20.86213871524472</v>
       </c>
       <c r="C5" t="n">
-        <v>38.9508401659922</v>
+        <v>116.1162097197915</v>
       </c>
       <c r="D5" t="n">
-        <v>30.60598467989432</v>
+        <v>39.90804417763285</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.55222523587222</v>
+        <v>14.12833121181585</v>
       </c>
       <c r="C6" t="n">
-        <v>22.09815907489146</v>
+        <v>109.726013912849</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>35.783722072092</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>14.43267300013236</v>
+        <v>47.90928796724435</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>37.06981156465531</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.071900272680289</v>
+        <v>17.32098756483433</v>
       </c>
       <c r="C21" t="n">
-        <v>67.18305259046275</v>
+        <v>114.3185179279066</v>
       </c>
       <c r="D21" t="n">
-        <v>5.303925204510217</v>
+        <v>4.330246891208583</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.928774385946488</v>
+        <v>2.451424017504285</v>
       </c>
       <c r="C2" t="n">
-        <v>5.65093978564464</v>
+        <v>9.595602061308325</v>
       </c>
       <c r="D2" t="n">
-        <v>25.9161758967073</v>
+        <v>18.77788833912874</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.00449213236051</v>
+        <v>7.451465075233291</v>
       </c>
       <c r="C3" t="n">
-        <v>21.54445336969626</v>
+        <v>27.58220175081414</v>
       </c>
       <c r="D3" t="n">
-        <v>57.38315331322607</v>
+        <v>55.84180941755857</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.68684784454105</v>
+        <v>15.0982979436117</v>
       </c>
       <c r="C4" t="n">
-        <v>45.70330087580177</v>
+        <v>71.29255478699488</v>
       </c>
       <c r="D4" t="n">
-        <v>60.34214089382595</v>
+        <v>67.77004402415733</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.90617849321559</v>
+        <v>22.92380889416302</v>
       </c>
       <c r="C5" t="n">
-        <v>56.13142499031139</v>
+        <v>118.5705789804085</v>
       </c>
       <c r="D5" t="n">
-        <v>39.93258787023902</v>
+        <v>50.06913291658734</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.05161602216436</v>
+        <v>20.56859615167493</v>
       </c>
       <c r="C6" t="n">
-        <v>46.249152599363</v>
+        <v>144.7047028674586</v>
       </c>
       <c r="D6" t="n">
-        <v>33.97239755775664</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.42027013287564</v>
+        <v>11.91743538185203</v>
       </c>
       <c r="C7" t="n">
-        <v>25.03260296288517</v>
+        <v>100.9688243909675</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>19.3600647277471</v>
+        <v>43.39324852770901</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.301089542085998</v>
+        <v>17.70914352649075</v>
       </c>
       <c r="C21" t="n">
-        <v>77.57407638466373</v>
+        <v>126.6203762144089</v>
       </c>
       <c r="D21" t="n">
-        <v>6.388453349325248</v>
+        <v>5.312743057947225</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.301036692305276</v>
+        <v>2.214822820780804</v>
       </c>
       <c r="C2" t="n">
-        <v>9.709484795000956</v>
+        <v>6.064255569132548</v>
       </c>
       <c r="D2" t="n">
-        <v>27.45162930614931</v>
+        <v>14.93532782470673</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.86213871524472</v>
+        <v>10.02364406035993</v>
       </c>
       <c r="C3" t="n">
-        <v>21.853703896534</v>
+        <v>44.01174958138451</v>
       </c>
       <c r="D3" t="n">
-        <v>65.28622233241289</v>
+        <v>61.5408548407113</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.31444666946201</v>
+        <v>11.01422749394496</v>
       </c>
       <c r="C4" t="n">
-        <v>50.78286349757476</v>
+        <v>102.9823889323777</v>
       </c>
       <c r="D4" t="n">
-        <v>76.4104055692335</v>
+        <v>63.03507484657496</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82749980815561</v>
+        <v>11.58462291011236</v>
       </c>
       <c r="C5" t="n">
-        <v>72.94385442553802</v>
+        <v>86.46742905153783</v>
       </c>
       <c r="D5" t="n">
-        <v>53.30890034060182</v>
+        <v>37.99363615435157</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>70.76241102670161</v>
+        <v>66.49573550404497</v>
       </c>
       <c r="D6" t="n">
-        <v>38.88309957439917</v>
+        <v>25.80131141531043</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>48.32849423695774</v>
+        <v>30.48228446915921</v>
       </c>
       <c r="D7" t="n">
-        <v>36.59071868498287</v>
+        <v>26.82920126165683</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>27.53802310412303</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>24.51718541815559</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.51923743108413</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.411135136353</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.51923743108413</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
